--- a/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/Org_rev2_best/DHTCUN+50T+50EP+optim_purn/params_vs_psnr_analysis/DHTCUN_baseline_hutcn_hyperopt_study_full.xlsx
+++ b/ملفات محدثةللاسترجاع/org_rev2/Hyperparameters_Obtimization/Org_rev2_best/DHTCUN+50T+50EP+optim_purn/params_vs_psnr_analysis/DHTCUN_baseline_hutcn_hyperopt_study_full.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N36"/>
+  <dimension ref="A1:O36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,55 +446,60 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>flops_G</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>hp_n_feats</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hp_num_heads</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>hp_depth</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>hp_window_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>hp_mlp_ratio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>hp_patch_size</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>hp_optimizer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>hp_scheduler</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>hp_loss</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>hp_lr</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>hp_weight_decay</t>
         </is>
@@ -511,42 +516,45 @@
         <v>26.83783912658691</v>
       </c>
       <c r="D2" t="n">
+        <v>2.718208332</v>
+      </c>
+      <c r="E2" t="n">
         <v>56</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>16</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>2.25</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>192</v>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>1.725821539662501e-05</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7.523742884534855e-06</v>
       </c>
     </row>
@@ -561,42 +569,45 @@
         <v>26.01563720703125</v>
       </c>
       <c r="D3" t="n">
+        <v>3.789107532</v>
+      </c>
+      <c r="E3" t="n">
         <v>56</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>4</v>
       </c>
-      <c r="F3" t="n">
-        <v>2</v>
-      </c>
       <c r="G3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" t="n">
         <v>16</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>1.5</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>192</v>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>2.752069685079051e-05</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>9.717775305059631e-05</v>
       </c>
     </row>
@@ -611,42 +622,45 @@
         <v>28.65984687805176</v>
       </c>
       <c r="D4" t="n">
+        <v>3.321879984</v>
+      </c>
+      <c r="E4" t="n">
         <v>48</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>4</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>12</v>
       </c>
-      <c r="H4" t="n">
-        <v>2</v>
-      </c>
       <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
         <v>128</v>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K4" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>0.0002306261812167793</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>1.673601016782579e-06</v>
       </c>
     </row>
@@ -661,42 +675,45 @@
         <v>27.24328155517578</v>
       </c>
       <c r="D5" t="n">
+        <v>12.045350592</v>
+      </c>
+      <c r="E5" t="n">
         <v>96</v>
       </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
       <c r="F5" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>16</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>1.5</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>192</v>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>1.596566588617374e-05</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>0.0001379540204020417</v>
       </c>
     </row>
@@ -711,42 +728,45 @@
         <v>26.10691719055176</v>
       </c>
       <c r="D6" t="n">
+        <v>5.45183352</v>
+      </c>
+      <c r="E6" t="n">
         <v>80</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>4</v>
       </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
       <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
         <v>8</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.5</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>128</v>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Huber</t>
         </is>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>0.000236032760012781</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>7.947147424653752e-05</v>
       </c>
     </row>
@@ -761,42 +781,45 @@
         <v>28.00007972717285</v>
       </c>
       <c r="D7" t="n">
+        <v>7.179103404</v>
+      </c>
+      <c r="E7" t="n">
         <v>88</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>8</v>
       </c>
-      <c r="F7" t="n">
-        <v>2</v>
-      </c>
       <c r="G7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" t="n">
         <v>12</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>1.5</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>192</v>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>7.610438922351127e-05</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>0.0001285454996487902</v>
       </c>
     </row>
@@ -811,42 +834,45 @@
         <v>28.01357231140137</v>
       </c>
       <c r="D8" t="n">
+        <v>3.014963532</v>
+      </c>
+      <c r="E8" t="n">
         <v>56</v>
       </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
       <c r="F8" t="n">
         <v>2</v>
       </c>
       <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
         <v>8</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>2.25</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>128</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>step</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>0.0001726703355444434</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>1.268672126210486e-05</v>
       </c>
     </row>
@@ -861,42 +887,45 @@
         <v>30.67520637512207</v>
       </c>
       <c r="D9" t="n">
+        <v>5.8936491</v>
+      </c>
+      <c r="E9" t="n">
         <v>72</v>
       </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
       <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
         <v>3</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>8</v>
       </c>
-      <c r="H9" t="n">
-        <v>2</v>
-      </c>
       <c r="I9" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" t="n">
         <v>128</v>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K9" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>0.0003724146189492819</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>0.0004285663419650346</v>
       </c>
     </row>
@@ -911,42 +940,45 @@
         <v>27.81236763000488</v>
       </c>
       <c r="D10" t="n">
+        <v>3.169263024</v>
+      </c>
+      <c r="E10" t="n">
         <v>48</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="F10" t="n">
-        <v>2</v>
-      </c>
       <c r="G10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" t="n">
         <v>16</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>2.5</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>128</v>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>1.036634157292471e-05</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>2.015647705936503e-06</v>
       </c>
     </row>
@@ -961,42 +993,45 @@
         <v>28.01769943237305</v>
       </c>
       <c r="D11" t="n">
+        <v>7.62551982</v>
+      </c>
+      <c r="E11" t="n">
         <v>72</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>3</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>16</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1.75</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>160</v>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>ADAM</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>0.0003277633122023723</v>
       </c>
-      <c r="N11" t="n">
+      <c r="O11" t="n">
         <v>7.823766455329715e-05</v>
       </c>
     </row>
@@ -1011,42 +1046,45 @@
         <v>30.04224357604981</v>
       </c>
       <c r="D12" t="n">
+        <v>0.7739107200000001</v>
+      </c>
+      <c r="E12" t="n">
         <v>32</v>
       </c>
-      <c r="E12" t="n">
-        <v>2</v>
-      </c>
       <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>8</v>
       </c>
-      <c r="H12" t="n">
-        <v>2</v>
-      </c>
       <c r="I12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" t="n">
         <v>160</v>
       </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K12" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>0.0004852822449408544</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>0.0009474948691215786</v>
       </c>
     </row>
@@ -1061,42 +1099,45 @@
         <v>30.10458297729492</v>
       </c>
       <c r="D13" t="n">
+        <v>0.7739107200000001</v>
+      </c>
+      <c r="E13" t="n">
         <v>32</v>
       </c>
-      <c r="E13" t="n">
-        <v>2</v>
-      </c>
       <c r="F13" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" t="n">
         <v>1</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>8</v>
       </c>
-      <c r="H13" t="n">
-        <v>2</v>
-      </c>
       <c r="I13" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" t="n">
         <v>160</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K13" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>0.000445083689741806</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>0.0009912574829445237</v>
       </c>
     </row>
@@ -1111,42 +1152,45 @@
         <v>30.14191131591797</v>
       </c>
       <c r="D14" t="n">
+        <v>3.46504878</v>
+      </c>
+      <c r="E14" t="n">
         <v>72</v>
       </c>
-      <c r="E14" t="n">
-        <v>2</v>
-      </c>
       <c r="F14" t="n">
+        <v>2</v>
+      </c>
+      <c r="G14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>8</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>1.75</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>160</v>
       </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K14" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>0.0001344751694139241</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>0.0003985750270846643</v>
       </c>
     </row>
@@ -1161,42 +1205,45 @@
         <v>30.26673736572265</v>
       </c>
       <c r="D15" t="n">
+        <v>5.71449006</v>
+      </c>
+      <c r="E15" t="n">
         <v>72</v>
       </c>
-      <c r="E15" t="n">
-        <v>2</v>
-      </c>
       <c r="F15" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" t="n">
         <v>3</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>8</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>1.75</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>128</v>
       </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>0.000123410998262688</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>0.000323748075129171</v>
       </c>
     </row>
@@ -1211,42 +1258,45 @@
         <v>29.63857574462891</v>
       </c>
       <c r="D16" t="n">
+        <v>5.71449006</v>
+      </c>
+      <c r="E16" t="n">
         <v>72</v>
       </c>
-      <c r="E16" t="n">
-        <v>2</v>
-      </c>
       <c r="F16" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>8</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>1.75</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>128</v>
       </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>4.641719714234165e-05</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>0.0002554391956428337</v>
       </c>
     </row>
@@ -1261,42 +1311,45 @@
         <v>30.41717414855957</v>
       </c>
       <c r="D17" t="n">
+        <v>9.299889324</v>
+      </c>
+      <c r="E17" t="n">
         <v>88</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>8</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>3</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>12</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>1.75</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>128</v>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K17" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>0.0001193782508761017</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>3.383838905912798e-05</v>
       </c>
     </row>
@@ -1311,42 +1364,45 @@
         <v>30.07740440368652</v>
       </c>
       <c r="D18" t="n">
+        <v>11.833013952</v>
+      </c>
+      <c r="E18" t="n">
         <v>96</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>8</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>3</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>12</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>2.5</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>128</v>
       </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>5.731756136786262e-05</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>2.7419500068863e-05</v>
       </c>
     </row>
@@ -1361,42 +1417,45 @@
         <v>30.40658302307129</v>
       </c>
       <c r="D19" t="n">
+        <v>9.567521964000001</v>
+      </c>
+      <c r="E19" t="n">
         <v>88</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>8</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>3</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>12</v>
       </c>
-      <c r="H19" t="n">
-        <v>2</v>
-      </c>
       <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
         <v>128</v>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
           <t>cosine</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>0.0001151329891615525</v>
       </c>
-      <c r="N19" t="n">
+      <c r="O19" t="n">
         <v>4.81939782427194e-06</v>
       </c>
     </row>
@@ -1411,42 +1470,45 @@
         <v>30.47558250427246</v>
       </c>
       <c r="D20" t="n">
+        <v>9.299889324</v>
+      </c>
+      <c r="E20" t="n">
         <v>88</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>8</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>3</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>12</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>1.75</v>
       </c>
-      <c r="I20" t="n">
+      <c r="J20" t="n">
         <v>128</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K20" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>L2</t>
         </is>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>0.0002919639139682338</v>
       </c>
-      <c r="N20" t="n">
+      <c r="O20" t="n">
         <v>3.520110236536836e-05</v>
       </c>
     </row>
@@ -1461,42 +1523,45 @@
         <v>30.56182022094726</v>
       </c>
       <c r="D21" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="E21" t="n">
         <v>80</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>8</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>3</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>12</v>
       </c>
-      <c r="H21" t="n">
-        <v>2</v>
-      </c>
       <c r="I21" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" t="n">
         <v>128</v>
       </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>0.0003441151929641435</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>3.42883585507601e-05</v>
       </c>
     </row>
@@ -1511,42 +1576,45 @@
         <v>30.61565399169922</v>
       </c>
       <c r="D22" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="E22" t="n">
         <v>80</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>8</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>12</v>
       </c>
-      <c r="H22" t="n">
-        <v>2</v>
-      </c>
       <c r="I22" t="n">
+        <v>2</v>
+      </c>
+      <c r="J22" t="n">
         <v>128</v>
       </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>0.0003035006991210817</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>3.350191404696732e-05</v>
       </c>
     </row>
@@ -1561,42 +1629,45 @@
         <v>30.60100364685059</v>
       </c>
       <c r="D23" t="n">
+        <v>8.065491120000001</v>
+      </c>
+      <c r="E23" t="n">
         <v>80</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>8</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>3</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>12</v>
       </c>
-      <c r="H23" t="n">
-        <v>2</v>
-      </c>
       <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="n">
         <v>128</v>
       </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>0.0003771249398726197</v>
       </c>
-      <c r="N23" t="n">
+      <c r="O23" t="n">
         <v>1.814170727733093e-05</v>
       </c>
     </row>
@@ -1611,42 +1682,45 @@
         <v>30.49831085205078</v>
       </c>
       <c r="D24" t="n">
+        <v>5.582340864</v>
+      </c>
+      <c r="E24" t="n">
         <v>64</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>3</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>12</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>2.25</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>128</v>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K24" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>0.0002246301446764361</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>1.337879865769602e-05</v>
       </c>
     </row>
@@ -1661,42 +1735,45 @@
         <v>30.52768745422363</v>
       </c>
       <c r="D25" t="n">
+        <v>6.33656952</v>
+      </c>
+      <c r="E25" t="n">
         <v>80</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>8</v>
       </c>
-      <c r="F25" t="n">
-        <v>2</v>
-      </c>
       <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
         <v>12</v>
       </c>
-      <c r="H25" t="n">
-        <v>2</v>
-      </c>
       <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="n">
         <v>128</v>
       </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K25" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>0.0003818588718189724</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>3.381371108418715e-06</v>
       </c>
     </row>
@@ -1711,42 +1788,45 @@
         <v>30.47917823791504</v>
       </c>
       <c r="D26" t="n">
+        <v>5.582340864</v>
+      </c>
+      <c r="E26" t="n">
         <v>64</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
         <v>8</v>
       </c>
-      <c r="F26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>12</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>2.25</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>128</v>
       </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>0.0001929029655809374</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>1.39917896480634e-05</v>
       </c>
     </row>
@@ -1761,42 +1841,45 @@
         <v>30.56425323486328</v>
       </c>
       <c r="D27" t="n">
+        <v>6.33656952</v>
+      </c>
+      <c r="E27" t="n">
         <v>80</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>8</v>
       </c>
-      <c r="F27" t="n">
-        <v>2</v>
-      </c>
       <c r="G27" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" t="n">
         <v>12</v>
       </c>
-      <c r="H27" t="n">
-        <v>2</v>
-      </c>
       <c r="I27" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" t="n">
         <v>128</v>
       </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>0.0004910096910182906</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>5.451388134282952e-05</v>
       </c>
     </row>
@@ -1811,42 +1894,45 @@
         <v>30.67307929992676</v>
       </c>
       <c r="D28" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="E28" t="n">
         <v>80</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>4</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>12</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>2.25</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>192</v>
       </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K28" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>0.0001500048440969381</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>1.096754845545604e-06</v>
       </c>
     </row>
@@ -1861,42 +1947,45 @@
         <v>30.66827926635742</v>
       </c>
       <c r="D29" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="E29" t="n">
         <v>80</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
         <v>4</v>
       </c>
-      <c r="F29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>12</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>2.25</v>
       </c>
-      <c r="I29" t="n">
+      <c r="J29" t="n">
         <v>192</v>
       </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>0.0003719226181397407</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>0.0005164287135341416</v>
       </c>
     </row>
@@ -1911,42 +2000,45 @@
         <v>30.80440101623535</v>
       </c>
       <c r="D30" t="n">
+        <v>8.28667512</v>
+      </c>
+      <c r="E30" t="n">
         <v>80</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>4</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>3</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>12</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>2.25</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>192</v>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>0.0002585883829298715</v>
       </c>
-      <c r="N30" t="n">
+      <c r="O30" t="n">
         <v>0.0004119537600595475</v>
       </c>
     </row>
@@ -1961,42 +2053,45 @@
         <v>30.74985580444336</v>
       </c>
       <c r="D31" t="n">
+        <v>9.835154604</v>
+      </c>
+      <c r="E31" t="n">
         <v>88</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>4</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>3</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>12</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>2.25</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>192</v>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>0.000154501901659111</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>0.0005021342196169607</v>
       </c>
     </row>
@@ -2011,42 +2106,45 @@
         <v>30.77203903198242</v>
       </c>
       <c r="D32" t="n">
+        <v>11.197648044</v>
+      </c>
+      <c r="E32" t="n">
         <v>88</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>4</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>3</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>16</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>2.25</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>192</v>
       </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>0.0002217370704340441</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>0.0002000469887748956</v>
       </c>
     </row>
@@ -2061,42 +2159,45 @@
         <v>30.6412036895752</v>
       </c>
       <c r="D33" t="n">
+        <v>8.622697644</v>
+      </c>
+      <c r="E33" t="n">
         <v>88</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>4</v>
       </c>
-      <c r="F33" t="n">
-        <v>2</v>
-      </c>
       <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
         <v>16</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>2.25</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>192</v>
       </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>0.0001967735196353697</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>0.0006074730225710179</v>
       </c>
     </row>
@@ -2111,42 +2212,45 @@
         <v>30.64308013916015</v>
       </c>
       <c r="D34" t="n">
+        <v>7.40193912</v>
+      </c>
+      <c r="E34" t="n">
         <v>80</v>
       </c>
-      <c r="E34" t="n">
+      <c r="F34" t="n">
         <v>4</v>
       </c>
-      <c r="F34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>8</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>2.25</v>
       </c>
-      <c r="I34" t="n">
+      <c r="J34" t="n">
         <v>192</v>
       </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>L1</t>
         </is>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>0.0001494605358877765</v>
       </c>
-      <c r="N34" t="n">
+      <c r="O34" t="n">
         <v>0.0001876070387487759</v>
       </c>
     </row>
@@ -2161,42 +2265,45 @@
         <v>30.74884223937988</v>
       </c>
       <c r="D35" t="n">
+        <v>9.52530552</v>
+      </c>
+      <c r="E35" t="n">
         <v>80</v>
       </c>
-      <c r="E35" t="n">
+      <c r="F35" t="n">
         <v>4</v>
       </c>
-      <c r="F35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>16</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>2.25</v>
       </c>
-      <c r="I35" t="n">
+      <c r="J35" t="n">
         <v>192</v>
       </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>0.0001742996594780831</v>
       </c>
-      <c r="N35" t="n">
+      <c r="O35" t="n">
         <v>0.0004291074301173133</v>
       </c>
     </row>
@@ -2211,42 +2318,45 @@
         <v>30.76295967102051</v>
       </c>
       <c r="D36" t="n">
+        <v>11.197648044</v>
+      </c>
+      <c r="E36" t="n">
         <v>88</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>4</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>16</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>2.25</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>192</v>
       </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>AdamW</t>
-        </is>
-      </c>
       <c r="K36" t="inlineStr">
         <is>
+          <t>AdamW</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
           <t>fixed</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Charbonnier</t>
         </is>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>0.0002014559080527861</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>0.0004826730542923709</v>
       </c>
     </row>
